--- a/Result/checksun/玻璃陶瓷.xlsx
+++ b/Result/checksun/玻璃陶瓷.xlsx
@@ -641,62 +641,62 @@
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>my_signal</t>
+          <t>up_up</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>my_signal_3d</t>
+          <t>up_up_3d</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>my_signal_5d</t>
+          <t>up_up_5d</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>my_signal_10d</t>
+          <t>up_up_10d</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>up_up</t>
+          <t>bbw_cross</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>up_up_3d</t>
+          <t>MA_UP_d</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>up_up_5d</t>
+          <t>MA_UP_3d</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>up_up_10d</t>
+          <t>MA_UP_5d</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>bbw_cross</t>
+          <t>MA_UP_10d</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>MA_UP_3d</t>
+          <t>MA_UP_20d</t>
         </is>
       </c>
       <c r="BA1" s="1" t="inlineStr">
         <is>
-          <t>MA_UP_5d</t>
+          <t>MA_UP_30d</t>
         </is>
       </c>
       <c r="BB1" s="1" t="inlineStr">
         <is>
-          <t>MA_UP_10d</t>
+          <t>MA_UP_40d</t>
         </is>
       </c>
       <c r="BC1" s="1" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
@@ -1683,22 +1683,22 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
@@ -1897,11 +1897,15 @@
           <t>40.15</t>
         </is>
       </c>
-      <c r="CQ2" t="n">
-        <v>40.16</v>
-      </c>
-      <c r="CR2" t="n">
-        <v>39.64</v>
+      <c r="CQ2" t="inlineStr">
+        <is>
+          <t>40.16</t>
+        </is>
+      </c>
+      <c r="CR2" t="inlineStr">
+        <is>
+          <t>39.64</t>
+        </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
@@ -2654,7 +2658,7 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
@@ -2664,27 +2668,27 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
@@ -2883,11 +2887,15 @@
           <t>40.185</t>
         </is>
       </c>
-      <c r="CQ3" t="n">
-        <v>40.18</v>
-      </c>
-      <c r="CR3" t="n">
-        <v>39.62</v>
+      <c r="CQ3" t="inlineStr">
+        <is>
+          <t>40.18</t>
+        </is>
+      </c>
+      <c r="CR3" t="inlineStr">
+        <is>
+          <t>39.62</t>
+        </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
@@ -3640,7 +3648,7 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
@@ -3650,27 +3658,27 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
@@ -3869,11 +3877,15 @@
           <t>40.205</t>
         </is>
       </c>
-      <c r="CQ4" t="n">
-        <v>40.2</v>
-      </c>
-      <c r="CR4" t="n">
-        <v>39.59</v>
+      <c r="CQ4" t="inlineStr">
+        <is>
+          <t>40.2</t>
+        </is>
+      </c>
+      <c r="CR4" t="inlineStr">
+        <is>
+          <t>39.59</t>
+        </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
@@ -4626,37 +4638,37 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
@@ -4855,11 +4867,15 @@
           <t>40.25</t>
         </is>
       </c>
-      <c r="CQ5" t="n">
-        <v>40.21</v>
-      </c>
-      <c r="CR5" t="n">
-        <v>39.56</v>
+      <c r="CQ5" t="inlineStr">
+        <is>
+          <t>40.21</t>
+        </is>
+      </c>
+      <c r="CR5" t="inlineStr">
+        <is>
+          <t>39.56</t>
+        </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
@@ -5612,37 +5628,37 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
@@ -5841,11 +5857,15 @@
           <t>40.31</t>
         </is>
       </c>
-      <c r="CQ6" t="n">
-        <v>40.24</v>
-      </c>
-      <c r="CR6" t="n">
-        <v>39.54</v>
+      <c r="CQ6" t="inlineStr">
+        <is>
+          <t>40.24</t>
+        </is>
+      </c>
+      <c r="CR6" t="inlineStr">
+        <is>
+          <t>39.54</t>
+        </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
@@ -6598,37 +6618,37 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
@@ -6827,11 +6847,15 @@
           <t>40.345</t>
         </is>
       </c>
-      <c r="CQ7" t="n">
-        <v>40.25</v>
-      </c>
-      <c r="CR7" t="n">
-        <v>39.51</v>
+      <c r="CQ7" t="inlineStr">
+        <is>
+          <t>40.25</t>
+        </is>
+      </c>
+      <c r="CR7" t="inlineStr">
+        <is>
+          <t>39.51</t>
+        </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
@@ -7584,37 +7608,37 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
@@ -7813,11 +7837,15 @@
           <t>40.305</t>
         </is>
       </c>
-      <c r="CQ8" t="n">
-        <v>40.24</v>
-      </c>
-      <c r="CR8" t="n">
-        <v>39.47</v>
+      <c r="CQ8" t="inlineStr">
+        <is>
+          <t>40.24</t>
+        </is>
+      </c>
+      <c r="CR8" t="inlineStr">
+        <is>
+          <t>39.47</t>
+        </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
@@ -8570,37 +8598,37 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
@@ -8799,11 +8827,15 @@
           <t>40.275</t>
         </is>
       </c>
-      <c r="CQ9" t="n">
-        <v>40.23</v>
-      </c>
-      <c r="CR9" t="n">
-        <v>39.43</v>
+      <c r="CQ9" t="inlineStr">
+        <is>
+          <t>40.23</t>
+        </is>
+      </c>
+      <c r="CR9" t="inlineStr">
+        <is>
+          <t>39.43</t>
+        </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
@@ -9556,37 +9588,37 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
@@ -9785,11 +9817,15 @@
           <t>40.235</t>
         </is>
       </c>
-      <c r="CQ10" t="n">
-        <v>40.2</v>
-      </c>
-      <c r="CR10" t="n">
-        <v>39.4</v>
+      <c r="CQ10" t="inlineStr">
+        <is>
+          <t>40.2</t>
+        </is>
+      </c>
+      <c r="CR10" t="inlineStr">
+        <is>
+          <t>39.4</t>
+        </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
@@ -10542,7 +10578,7 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
@@ -10557,7 +10593,7 @@
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
@@ -10771,11 +10807,15 @@
           <t>23.94</t>
         </is>
       </c>
-      <c r="CQ11" t="n">
-        <v>23.88</v>
-      </c>
-      <c r="CR11" t="n">
-        <v>24.81</v>
+      <c r="CQ11" t="inlineStr">
+        <is>
+          <t>23.88</t>
+        </is>
+      </c>
+      <c r="CR11" t="inlineStr">
+        <is>
+          <t>24.81</t>
+        </is>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
@@ -11528,7 +11568,7 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
@@ -11543,7 +11583,7 @@
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
@@ -11757,11 +11797,15 @@
           <t>23.895</t>
         </is>
       </c>
-      <c r="CQ12" t="n">
-        <v>23.92</v>
-      </c>
-      <c r="CR12" t="n">
-        <v>25.02</v>
+      <c r="CQ12" t="inlineStr">
+        <is>
+          <t>23.92</t>
+        </is>
+      </c>
+      <c r="CR12" t="inlineStr">
+        <is>
+          <t>25.02</t>
+        </is>
       </c>
       <c r="CS12" t="inlineStr">
         <is>
@@ -12514,7 +12558,7 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
@@ -12529,7 +12573,7 @@
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
@@ -12743,11 +12787,15 @@
           <t>23.84</t>
         </is>
       </c>
-      <c r="CQ13" t="n">
-        <v>23.96</v>
-      </c>
-      <c r="CR13" t="n">
-        <v>25.16</v>
+      <c r="CQ13" t="inlineStr">
+        <is>
+          <t>23.96</t>
+        </is>
+      </c>
+      <c r="CR13" t="inlineStr">
+        <is>
+          <t>25.16</t>
+        </is>
       </c>
       <c r="CS13" t="inlineStr">
         <is>
@@ -13500,7 +13548,7 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
@@ -13515,7 +13563,7 @@
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
@@ -13729,11 +13777,15 @@
           <t>23.775</t>
         </is>
       </c>
-      <c r="CQ14" t="n">
-        <v>23.98</v>
-      </c>
-      <c r="CR14" t="n">
-        <v>25.24</v>
+      <c r="CQ14" t="inlineStr">
+        <is>
+          <t>23.98</t>
+        </is>
+      </c>
+      <c r="CR14" t="inlineStr">
+        <is>
+          <t>25.24</t>
+        </is>
       </c>
       <c r="CS14" t="inlineStr">
         <is>
@@ -14486,7 +14538,7 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
@@ -14501,7 +14553,7 @@
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
@@ -14715,11 +14767,15 @@
           <t>23.76</t>
         </is>
       </c>
-      <c r="CQ15" t="n">
-        <v>24.06</v>
-      </c>
-      <c r="CR15" t="n">
-        <v>25.3</v>
+      <c r="CQ15" t="inlineStr">
+        <is>
+          <t>24.06</t>
+        </is>
+      </c>
+      <c r="CR15" t="inlineStr">
+        <is>
+          <t>25.3</t>
+        </is>
       </c>
       <c r="CS15" t="inlineStr">
         <is>
@@ -15472,7 +15528,7 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
@@ -15487,7 +15543,7 @@
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
@@ -15701,11 +15757,15 @@
           <t>23.735</t>
         </is>
       </c>
-      <c r="CQ16" t="n">
-        <v>24.15</v>
-      </c>
-      <c r="CR16" t="n">
-        <v>25.4</v>
+      <c r="CQ16" t="inlineStr">
+        <is>
+          <t>24.15</t>
+        </is>
+      </c>
+      <c r="CR16" t="inlineStr">
+        <is>
+          <t>25.4</t>
+        </is>
       </c>
       <c r="CS16" t="inlineStr">
         <is>
@@ -16458,7 +16518,7 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
@@ -16473,7 +16533,7 @@
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
@@ -16687,11 +16747,15 @@
           <t>23.75</t>
         </is>
       </c>
-      <c r="CQ17" t="n">
-        <v>24.24</v>
-      </c>
-      <c r="CR17" t="n">
-        <v>25.55</v>
+      <c r="CQ17" t="inlineStr">
+        <is>
+          <t>24.24</t>
+        </is>
+      </c>
+      <c r="CR17" t="inlineStr">
+        <is>
+          <t>25.55</t>
+        </is>
       </c>
       <c r="CS17" t="inlineStr">
         <is>
@@ -17444,7 +17508,7 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
@@ -17459,7 +17523,7 @@
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
@@ -17673,11 +17737,15 @@
           <t>23.765</t>
         </is>
       </c>
-      <c r="CQ18" t="n">
-        <v>24.28</v>
-      </c>
-      <c r="CR18" t="n">
-        <v>25.65</v>
+      <c r="CQ18" t="inlineStr">
+        <is>
+          <t>24.28</t>
+        </is>
+      </c>
+      <c r="CR18" t="inlineStr">
+        <is>
+          <t>25.65</t>
+        </is>
       </c>
       <c r="CS18" t="inlineStr">
         <is>
@@ -18430,7 +18498,7 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
@@ -18445,7 +18513,7 @@
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
@@ -18659,11 +18727,15 @@
           <t>23.78</t>
         </is>
       </c>
-      <c r="CQ19" t="n">
-        <v>24.34</v>
-      </c>
-      <c r="CR19" t="n">
-        <v>25.69</v>
+      <c r="CQ19" t="inlineStr">
+        <is>
+          <t>24.34</t>
+        </is>
+      </c>
+      <c r="CR19" t="inlineStr">
+        <is>
+          <t>25.69</t>
+        </is>
       </c>
       <c r="CS19" t="inlineStr">
         <is>
@@ -19391,62 +19463,62 @@
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS20" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AR20" t="inlineStr">
+      <c r="AV20" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AW20" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AS20" t="inlineStr">
+      <c r="AX20" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="AT20" t="inlineStr">
-        <is>
-          <t>6.0</t>
-        </is>
-      </c>
-      <c r="AU20" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV20" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AW20" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
@@ -19645,11 +19717,15 @@
           <t>42.825</t>
         </is>
       </c>
-      <c r="CQ20" t="n">
-        <v>40.2</v>
-      </c>
-      <c r="CR20" t="n">
-        <v>38.75</v>
+      <c r="CQ20" t="inlineStr">
+        <is>
+          <t>40.2</t>
+        </is>
+      </c>
+      <c r="CR20" t="inlineStr">
+        <is>
+          <t>38.75</t>
+        </is>
       </c>
       <c r="CS20" t="inlineStr">
         <is>
@@ -20377,62 +20453,62 @@
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS21" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AR21" t="inlineStr">
+      <c r="AV21" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AW21" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AS21" t="inlineStr">
+      <c r="AX21" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="AT21" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="AU21" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV21" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AW21" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
@@ -20631,11 +20707,15 @@
           <t>41.8</t>
         </is>
       </c>
-      <c r="CQ21" t="n">
-        <v>39.74</v>
-      </c>
-      <c r="CR21" t="n">
-        <v>38.6</v>
+      <c r="CQ21" t="inlineStr">
+        <is>
+          <t>39.74</t>
+        </is>
+      </c>
+      <c r="CR21" t="inlineStr">
+        <is>
+          <t>38.6</t>
+        </is>
       </c>
       <c r="CS21" t="inlineStr">
         <is>
@@ -21363,62 +21443,62 @@
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AS22" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AR22" t="inlineStr">
+      <c r="AV22" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AW22" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AS22" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="AT22" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="AU22" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV22" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AW22" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
@@ -21617,11 +21697,15 @@
           <t>40.825</t>
         </is>
       </c>
-      <c r="CQ22" t="n">
-        <v>39.4</v>
-      </c>
-      <c r="CR22" t="n">
-        <v>38.46</v>
+      <c r="CQ22" t="inlineStr">
+        <is>
+          <t>39.4</t>
+        </is>
+      </c>
+      <c r="CR22" t="inlineStr">
+        <is>
+          <t>38.46</t>
+        </is>
       </c>
       <c r="CS22" t="inlineStr">
         <is>
@@ -22349,62 +22433,62 @@
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AS23" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AR23" t="inlineStr">
+      <c r="AV23" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AW23" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AS23" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="AT23" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="AU23" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV23" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AW23" t="inlineStr">
+      <c r="AX23" t="inlineStr">
         <is>
           <t>4.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
+      <c r="AY23" t="inlineStr">
         <is>
           <t>4.0</t>
         </is>
       </c>
-      <c r="AY23" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
@@ -22603,11 +22687,15 @@
           <t>39.73999999999999</t>
         </is>
       </c>
-      <c r="CQ23" t="n">
-        <v>38.96</v>
-      </c>
-      <c r="CR23" t="n">
-        <v>38.26</v>
+      <c r="CQ23" t="inlineStr">
+        <is>
+          <t>38.96</t>
+        </is>
+      </c>
+      <c r="CR23" t="inlineStr">
+        <is>
+          <t>38.26</t>
+        </is>
       </c>
       <c r="CS23" t="inlineStr">
         <is>
@@ -23340,17 +23428,17 @@
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AU24" t="inlineStr">
@@ -23360,37 +23448,37 @@
       </c>
       <c r="AV24" t="inlineStr">
         <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AW24" t="inlineStr">
+        <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AW24" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BC24" t="inlineStr">
@@ -23589,11 +23677,15 @@
           <t>38.985</t>
         </is>
       </c>
-      <c r="CQ24" t="n">
-        <v>38.69</v>
-      </c>
-      <c r="CR24" t="n">
-        <v>38.16</v>
+      <c r="CQ24" t="inlineStr">
+        <is>
+          <t>38.69</t>
+        </is>
+      </c>
+      <c r="CR24" t="inlineStr">
+        <is>
+          <t>38.16</t>
+        </is>
       </c>
       <c r="CS24" t="inlineStr">
         <is>
@@ -24326,17 +24418,17 @@
       </c>
       <c r="AR25" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AU25" t="inlineStr">
@@ -24346,37 +24438,37 @@
       </c>
       <c r="AV25" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BB25" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BC25" t="inlineStr">
@@ -24575,11 +24667,15 @@
           <t>38.255</t>
         </is>
       </c>
-      <c r="CQ25" t="n">
-        <v>38.39</v>
-      </c>
-      <c r="CR25" t="n">
-        <v>38.13</v>
+      <c r="CQ25" t="inlineStr">
+        <is>
+          <t>38.39</t>
+        </is>
+      </c>
+      <c r="CR25" t="inlineStr">
+        <is>
+          <t>38.13</t>
+        </is>
       </c>
       <c r="CS25" t="inlineStr">
         <is>
@@ -25307,62 +25403,62 @@
       </c>
       <c r="AQ26" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AU26" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV26" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AV26" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BC26" t="inlineStr">
@@ -25561,11 +25657,15 @@
           <t>38.02999999999999</t>
         </is>
       </c>
-      <c r="CQ26" t="n">
-        <v>38.33</v>
-      </c>
-      <c r="CR26" t="n">
-        <v>38.21</v>
+      <c r="CQ26" t="inlineStr">
+        <is>
+          <t>38.33</t>
+        </is>
+      </c>
+      <c r="CR26" t="inlineStr">
+        <is>
+          <t>38.21</t>
+        </is>
       </c>
       <c r="CS26" t="inlineStr">
         <is>
@@ -26293,62 +26393,62 @@
       </c>
       <c r="AQ27" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AR27" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AU27" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV27" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AV27" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BB27" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BC27" t="inlineStr">
@@ -26547,11 +26647,15 @@
           <t>37.78</t>
         </is>
       </c>
-      <c r="CQ27" t="n">
-        <v>38.18</v>
-      </c>
-      <c r="CR27" t="n">
-        <v>38.32</v>
+      <c r="CQ27" t="inlineStr">
+        <is>
+          <t>38.18</t>
+        </is>
+      </c>
+      <c r="CR27" t="inlineStr">
+        <is>
+          <t>38.32</t>
+        </is>
       </c>
       <c r="CS27" t="inlineStr">
         <is>
@@ -27304,7 +27408,7 @@
       </c>
       <c r="AV28" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW28" t="inlineStr">
@@ -27319,22 +27423,22 @@
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BB28" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BC28" t="inlineStr">
@@ -27533,11 +27637,15 @@
           <t>37.67</t>
         </is>
       </c>
-      <c r="CQ28" t="n">
-        <v>38.12</v>
-      </c>
-      <c r="CR28" t="n">
-        <v>38.49</v>
+      <c r="CQ28" t="inlineStr">
+        <is>
+          <t>38.12</t>
+        </is>
+      </c>
+      <c r="CR28" t="inlineStr">
+        <is>
+          <t>38.49</t>
+        </is>
       </c>
       <c r="CS28" t="inlineStr">
         <is>
@@ -28290,7 +28398,7 @@
       </c>
       <c r="AV29" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW29" t="inlineStr">
@@ -28305,22 +28413,22 @@
       </c>
       <c r="AY29" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BB29" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BC29" t="inlineStr">
@@ -28519,11 +28627,15 @@
           <t>7.972</t>
         </is>
       </c>
-      <c r="CQ29" t="n">
-        <v>7.99</v>
-      </c>
-      <c r="CR29" t="n">
-        <v>8.01</v>
+      <c r="CQ29" t="inlineStr">
+        <is>
+          <t>7.99</t>
+        </is>
+      </c>
+      <c r="CR29" t="inlineStr">
+        <is>
+          <t>8.01</t>
+        </is>
       </c>
       <c r="CS29" t="inlineStr">
         <is>
@@ -29276,7 +29388,7 @@
       </c>
       <c r="AV30" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW30" t="inlineStr">
@@ -29291,22 +29403,22 @@
       </c>
       <c r="AY30" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BB30" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BC30" t="inlineStr">
@@ -29505,11 +29617,15 @@
           <t>7.98</t>
         </is>
       </c>
-      <c r="CQ30" t="n">
-        <v>8</v>
-      </c>
-      <c r="CR30" t="n">
-        <v>8.02</v>
+      <c r="CQ30" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="CR30" t="inlineStr">
+        <is>
+          <t>8.02</t>
+        </is>
       </c>
       <c r="CS30" t="inlineStr">
         <is>
@@ -30262,7 +30378,7 @@
       </c>
       <c r="AV31" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW31" t="inlineStr">
@@ -30277,22 +30393,22 @@
       </c>
       <c r="AY31" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BB31" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BC31" t="inlineStr">
@@ -30491,11 +30607,15 @@
           <t>7.987</t>
         </is>
       </c>
-      <c r="CQ31" t="n">
-        <v>8.01</v>
-      </c>
-      <c r="CR31" t="n">
-        <v>8.029999999999999</v>
+      <c r="CQ31" t="inlineStr">
+        <is>
+          <t>8.01</t>
+        </is>
+      </c>
+      <c r="CR31" t="inlineStr">
+        <is>
+          <t>8.03</t>
+        </is>
       </c>
       <c r="CS31" t="inlineStr">
         <is>
@@ -31248,7 +31368,7 @@
       </c>
       <c r="AV32" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW32" t="inlineStr">
@@ -31263,22 +31383,22 @@
       </c>
       <c r="AY32" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BB32" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BC32" t="inlineStr">
@@ -31477,11 +31597,15 @@
           <t>7.985000000000001</t>
         </is>
       </c>
-      <c r="CQ32" t="n">
-        <v>8.01</v>
-      </c>
-      <c r="CR32" t="n">
-        <v>8.029999999999999</v>
+      <c r="CQ32" t="inlineStr">
+        <is>
+          <t>8.01</t>
+        </is>
+      </c>
+      <c r="CR32" t="inlineStr">
+        <is>
+          <t>8.03</t>
+        </is>
       </c>
       <c r="CS32" t="inlineStr">
         <is>
@@ -32234,7 +32358,7 @@
       </c>
       <c r="AV33" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW33" t="inlineStr">
@@ -32249,22 +32373,22 @@
       </c>
       <c r="AY33" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BB33" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BC33" t="inlineStr">
@@ -32463,11 +32587,15 @@
           <t>7.994</t>
         </is>
       </c>
-      <c r="CQ33" t="n">
-        <v>8.01</v>
-      </c>
-      <c r="CR33" t="n">
-        <v>8.039999999999999</v>
+      <c r="CQ33" t="inlineStr">
+        <is>
+          <t>8.01</t>
+        </is>
+      </c>
+      <c r="CR33" t="inlineStr">
+        <is>
+          <t>8.04</t>
+        </is>
       </c>
       <c r="CS33" t="inlineStr">
         <is>
@@ -33220,7 +33348,7 @@
       </c>
       <c r="AV34" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW34" t="inlineStr">
@@ -33235,22 +33363,22 @@
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BB34" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BC34" t="inlineStr">
@@ -33449,11 +33577,15 @@
           <t>7.999000000000001</t>
         </is>
       </c>
-      <c r="CQ34" t="n">
-        <v>8.01</v>
-      </c>
-      <c r="CR34" t="n">
-        <v>8.050000000000001</v>
+      <c r="CQ34" t="inlineStr">
+        <is>
+          <t>8.01</t>
+        </is>
+      </c>
+      <c r="CR34" t="inlineStr">
+        <is>
+          <t>8.05</t>
+        </is>
       </c>
       <c r="CS34" t="inlineStr">
         <is>
@@ -34206,7 +34338,7 @@
       </c>
       <c r="AV35" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW35" t="inlineStr">
@@ -34221,22 +34353,22 @@
       </c>
       <c r="AY35" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BB35" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BC35" t="inlineStr">
@@ -34435,11 +34567,15 @@
           <t>8.001999999999999</t>
         </is>
       </c>
-      <c r="CQ35" t="n">
-        <v>8.02</v>
-      </c>
-      <c r="CR35" t="n">
-        <v>8.050000000000001</v>
+      <c r="CQ35" t="inlineStr">
+        <is>
+          <t>8.02</t>
+        </is>
+      </c>
+      <c r="CR35" t="inlineStr">
+        <is>
+          <t>8.05</t>
+        </is>
       </c>
       <c r="CS35" t="inlineStr">
         <is>
@@ -35192,7 +35328,7 @@
       </c>
       <c r="AV36" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW36" t="inlineStr">
@@ -35207,22 +35343,22 @@
       </c>
       <c r="AY36" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BB36" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BC36" t="inlineStr">
@@ -35421,11 +35557,15 @@
           <t>8.007</t>
         </is>
       </c>
-      <c r="CQ36" t="n">
-        <v>8.02</v>
-      </c>
-      <c r="CR36" t="n">
-        <v>8.06</v>
+      <c r="CQ36" t="inlineStr">
+        <is>
+          <t>8.02</t>
+        </is>
+      </c>
+      <c r="CR36" t="inlineStr">
+        <is>
+          <t>8.06</t>
+        </is>
       </c>
       <c r="CS36" t="inlineStr">
         <is>
@@ -36178,7 +36318,7 @@
       </c>
       <c r="AV37" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW37" t="inlineStr">
@@ -36193,22 +36333,22 @@
       </c>
       <c r="AY37" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BB37" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BC37" t="inlineStr">
@@ -36407,11 +36547,15 @@
           <t>8.01</t>
         </is>
       </c>
-      <c r="CQ37" t="n">
-        <v>8.02</v>
-      </c>
-      <c r="CR37" t="n">
-        <v>8.06</v>
+      <c r="CQ37" t="inlineStr">
+        <is>
+          <t>8.02</t>
+        </is>
+      </c>
+      <c r="CR37" t="inlineStr">
+        <is>
+          <t>8.06</t>
+        </is>
       </c>
       <c r="CS37" t="inlineStr">
         <is>
@@ -37164,7 +37308,7 @@
       </c>
       <c r="AV38" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW38" t="inlineStr">
@@ -37179,22 +37323,22 @@
       </c>
       <c r="AY38" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BB38" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BC38" t="inlineStr">
@@ -37393,11 +37537,15 @@
           <t>58.8</t>
         </is>
       </c>
-      <c r="CQ38" t="n">
-        <v>58.83</v>
-      </c>
-      <c r="CR38" t="n">
-        <v>56.49</v>
+      <c r="CQ38" t="inlineStr">
+        <is>
+          <t>58.83</t>
+        </is>
+      </c>
+      <c r="CR38" t="inlineStr">
+        <is>
+          <t>56.49</t>
+        </is>
       </c>
       <c r="CS38" t="inlineStr">
         <is>
@@ -38150,7 +38298,7 @@
       </c>
       <c r="AV39" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW39" t="inlineStr">
@@ -38165,22 +38313,22 @@
       </c>
       <c r="AY39" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BB39" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BC39" t="inlineStr">
@@ -38379,11 +38527,15 @@
           <t>58.7</t>
         </is>
       </c>
-      <c r="CQ39" t="n">
-        <v>58.9</v>
-      </c>
-      <c r="CR39" t="n">
-        <v>56.41</v>
+      <c r="CQ39" t="inlineStr">
+        <is>
+          <t>58.9</t>
+        </is>
+      </c>
+      <c r="CR39" t="inlineStr">
+        <is>
+          <t>56.41</t>
+        </is>
       </c>
       <c r="CS39" t="inlineStr">
         <is>
@@ -39136,7 +39288,7 @@
       </c>
       <c r="AV40" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW40" t="inlineStr">
@@ -39151,22 +39303,22 @@
       </c>
       <c r="AY40" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BB40" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BC40" t="inlineStr">
@@ -39365,11 +39517,15 @@
           <t>58.42</t>
         </is>
       </c>
-      <c r="CQ40" t="n">
-        <v>59.02</v>
-      </c>
-      <c r="CR40" t="n">
-        <v>56.32</v>
+      <c r="CQ40" t="inlineStr">
+        <is>
+          <t>59.02</t>
+        </is>
+      </c>
+      <c r="CR40" t="inlineStr">
+        <is>
+          <t>56.32</t>
+        </is>
       </c>
       <c r="CS40" t="inlineStr">
         <is>
@@ -40122,7 +40278,7 @@
       </c>
       <c r="AV41" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW41" t="inlineStr">
@@ -40137,22 +40293,22 @@
       </c>
       <c r="AY41" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BB41" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BC41" t="inlineStr">
@@ -40351,11 +40507,15 @@
           <t>58.21</t>
         </is>
       </c>
-      <c r="CQ41" t="n">
-        <v>59.06</v>
-      </c>
-      <c r="CR41" t="n">
-        <v>56.19</v>
+      <c r="CQ41" t="inlineStr">
+        <is>
+          <t>59.06</t>
+        </is>
+      </c>
+      <c r="CR41" t="inlineStr">
+        <is>
+          <t>56.19</t>
+        </is>
       </c>
       <c r="CS41" t="inlineStr">
         <is>
@@ -41108,7 +41268,7 @@
       </c>
       <c r="AV42" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW42" t="inlineStr">
@@ -41123,22 +41283,22 @@
       </c>
       <c r="AY42" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BB42" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BC42" t="inlineStr">
@@ -41337,11 +41497,15 @@
           <t>58.27</t>
         </is>
       </c>
-      <c r="CQ42" t="n">
-        <v>59.22</v>
-      </c>
-      <c r="CR42" t="n">
-        <v>56.17</v>
+      <c r="CQ42" t="inlineStr">
+        <is>
+          <t>59.22</t>
+        </is>
+      </c>
+      <c r="CR42" t="inlineStr">
+        <is>
+          <t>56.17</t>
+        </is>
       </c>
       <c r="CS42" t="inlineStr">
         <is>
@@ -42094,7 +42258,7 @@
       </c>
       <c r="AV43" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW43" t="inlineStr">
@@ -42109,22 +42273,22 @@
       </c>
       <c r="AY43" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BB43" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BC43" t="inlineStr">
@@ -42323,11 +42487,15 @@
           <t>58.39</t>
         </is>
       </c>
-      <c r="CQ43" t="n">
-        <v>59.26</v>
-      </c>
-      <c r="CR43" t="n">
-        <v>56.23</v>
+      <c r="CQ43" t="inlineStr">
+        <is>
+          <t>59.26</t>
+        </is>
+      </c>
+      <c r="CR43" t="inlineStr">
+        <is>
+          <t>56.23</t>
+        </is>
       </c>
       <c r="CS43" t="inlineStr">
         <is>
@@ -43080,7 +43248,7 @@
       </c>
       <c r="AV44" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW44" t="inlineStr">
@@ -43095,22 +43263,22 @@
       </c>
       <c r="AY44" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BB44" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BC44" t="inlineStr">
@@ -43309,11 +43477,15 @@
           <t>58.65</t>
         </is>
       </c>
-      <c r="CQ44" t="n">
-        <v>59.37</v>
-      </c>
-      <c r="CR44" t="n">
-        <v>56.34</v>
+      <c r="CQ44" t="inlineStr">
+        <is>
+          <t>59.37</t>
+        </is>
+      </c>
+      <c r="CR44" t="inlineStr">
+        <is>
+          <t>56.34</t>
+        </is>
       </c>
       <c r="CS44" t="inlineStr">
         <is>
@@ -44066,7 +44238,7 @@
       </c>
       <c r="AV45" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW45" t="inlineStr">
@@ -44081,22 +44253,22 @@
       </c>
       <c r="AY45" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BB45" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BC45" t="inlineStr">
@@ -44295,11 +44467,15 @@
           <t>58.76000000000001</t>
         </is>
       </c>
-      <c r="CQ45" t="n">
-        <v>59.33</v>
-      </c>
-      <c r="CR45" t="n">
-        <v>56.42</v>
+      <c r="CQ45" t="inlineStr">
+        <is>
+          <t>59.33</t>
+        </is>
+      </c>
+      <c r="CR45" t="inlineStr">
+        <is>
+          <t>56.42</t>
+        </is>
       </c>
       <c r="CS45" t="inlineStr">
         <is>
@@ -45052,7 +45228,7 @@
       </c>
       <c r="AV46" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW46" t="inlineStr">
@@ -45067,22 +45243,22 @@
       </c>
       <c r="AY46" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BB46" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BC46" t="inlineStr">
@@ -45281,11 +45457,15 @@
           <t>58.82000000000001</t>
         </is>
       </c>
-      <c r="CQ46" t="n">
-        <v>59.17</v>
-      </c>
-      <c r="CR46" t="n">
-        <v>56.5</v>
+      <c r="CQ46" t="inlineStr">
+        <is>
+          <t>59.17</t>
+        </is>
+      </c>
+      <c r="CR46" t="inlineStr">
+        <is>
+          <t>56.5</t>
+        </is>
       </c>
       <c r="CS46" t="inlineStr">
         <is>
